--- a/final_integrated_analysis.xlsx
+++ b/final_integrated_analysis.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -773,7 +773,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>46136.00536965278</v>
@@ -1071,6 +1071,1226 @@
         <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
+        <is>
+          <t>L1_Native</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>36862</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Chinese (Simplified)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>task_b</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Invalid Response, Less Than 50 Words</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-04-29T00:56:03.979Z</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>36</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>46141.03989951389</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>46141.04110711806</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>204</v>
+      </c>
+      <c r="R8" t="n">
+        <v>16</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>58</v>
+      </c>
+      <c r="U8" t="n">
+        <v>104.337</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>L1_Native</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>36862</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>task_a</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intro: State the problem of housing costs outpacing income growth
+Policy Solution:
+1. Governments can use rent stabilization to limit extreme rent increases and protect low-income tenants from sudden displacement. 
+- For example, caps on annual rent growth can help families remain near jobs and schools. 
+- However, strict rent control may discourage landlords from maintaining units or reduce incentives to build new housing.
+2. Governments can increase housing supply through zoning reform, tax incentives, and affordable-unit requirements in new developments. 
+- This can lower long-term price pressure and support economic stability by helping workers live near employment centers. 
+- The trade-off is that construction takes time, requires funding, and may face community opposition. Overall, governments should combine tenant protections with more housing production.
+</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-04-29T01:00:28.392Z</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>124</v>
+      </c>
+      <c r="I9" t="n">
+        <v>876</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>46141.04352760417</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>46141.04487689815</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>524</v>
+      </c>
+      <c r="R9" t="n">
+        <v>74</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>374</v>
+      </c>
+      <c r="U9" t="n">
+        <v>116.579</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>L2_English</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UID-1777679608854-169na</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>task_b</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Managing Urban Overcrowding: Solutions for Sustainable Growth
+I. Introduction
+Overpopulation in urban areas presents complex challenges, requiring governments to prioritize sustainable solutions that balance affordability, opportunity, and quality of life. This outline explores two key policy approaches to managing urban overcrowding while fostering economic prosperity and citizen well-being.
+II. Expanding Affordable Housing &amp; Improving Urban Planning
+Policy: Investing in affordable housing construction and promoting mixed-use development.
+Rationale: Densely populated areas often lack affordable housing options, driving up costs and creating affordability challenges for residents. Mixed-use developments, where residential spaces share facilities with commercial or recreational offerings, can reduce commute times, promote local businesses, and increase overall efficiency of urban space.
+Example: Singapore uses public housing programs (like HDB flats) to provide affordable living spaces for a significant population within the city-state.
+Trade-offs: Construction projects require substantial funding and may face resistance from residents concerned about changes in neighborhood aesthetics or existing infrastructure.
+III. Investing in Public Transportation &amp; Regional Development
+Policy: Enhancing public transportation infrastructure (subways, buses) and encouraging decentralization by promoting regional development.
+Rationale: Improved public transportation reduces traffic congestion, minimizes pollution levels, and makes urban centers more accessible to residents. Governments can incentivize businesses to relocate to smaller cities by offering tax breaks or creating job opportunities in those regions.
+Example: Countries like Sweden have implemented policies that promote remote work and decentralization of businesses. This approach encourages economic activity outside major urban centers while reducing the strain on existing infrastructure in overcrowded cities.
+Trade-offs: Implementing robust public transportation systems requires long-term planning, financial investment, and may face challenges in achieving optimal coverage throughout a city or region. Attracting businesses to smaller towns requires significant government effort and time.
+IV. Combining Strategies for Sustainable Growth
+Conclusion: A combination of housing policy solutions like building more affordable housing alongside transportation improvements and regional development initiatives can create the most sustainable path forward. By prioritizing efficient urban planning, governments can address overcrowding while fostering economic opportunity and maintaining quality of life for citizens.
+↻
+This is my outline
+Edit
+</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-01T23:56:28.312Z</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>343</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2727</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>46144.00893046297</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>46144.01380280092</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1077</v>
+      </c>
+      <c r="R10" t="n">
+        <v>29</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>48</v>
+      </c>
+      <c r="U10" t="n">
+        <v>420.97</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>L2_English</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>36931</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>task_a</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>I. Expanding Housing Supply:
+A. Increase Density &amp; Mixed-Use Development:
+Reasoning:
+Encourage denser urban living by permitting multi-family construction and mixed-use zoning (e.g., residential, retail, office on the same property). This minimizes land usage for a larger population while creating walkable communities, reducing commuting costs.
+Example:
+Cities like Vancouver, Canada have implemented density bonuses for developers who build affordable units as part of larger projects.
+Trade-off:
+Increased density can cause community strain on infrastructure (schools, transportation) requiring proactive planning and funding for long-term maintenance.
+B. Invest in Affordable Housing Construction:
+Reasoning:
+Direct government investment through subsidies or tax breaks incentivizes private developers to build affordable units. This addresses both demand and supply gaps, ensuring a diverse housing market.
+Example:
+The "Housing Trust Fund" model used by various states provides direct funding for affordable housing construction.
+Trade-off:
+Government funds are finite; careful allocation is essential to maximize impact and avoid creating dependency on public assistance.
+II. Addressing Housing Costs:
+A. Rent Control &amp; Moratoriums:
+Reasoning:
+Temporary restrictions on rent increases can help stabilize housing prices for renters, especially in high-demand areas.
+Example:
+Many European countries have implemented rent control systems to prevent rapid price hikes and protect tenants from displacement.
+Trade-off:
+Rent controls can stifle property investment and potentially lead to decreased landlord maintenance, impacting overall building quality and long-term sustainability.
+B. Tax Incentives &amp; Rezoning:
+Reasoning:
+Tax breaks for first-time homebuyers or incentives for landlords offering rent subsidies could stimulate homeownership and incentivize investment in affordable housing projects.
+Example:
+Several cities offer tax deductions for down payment assistance to encourage greater participation in homebuying.
+Trade-off:
+These policies need careful design to avoid unintended consequences like inflated housing prices for those who can afford them or disproportionately benefiting wealthier demographics.
+Important Considerations:
+Data-Driven Approach: Government policy must be informed by accurate data about local housing needs, income levels, and market dynamics.
+Collaboration: Multi-pronged solutions are needed – combining supply-side changes with direct support for renters and homeowners to achieve lasting impact.
+Transparency &amp; Public Engagement: Open dialogue between government officials, developers, and community groups is crucial to ensure policies reflect local needs and concerns.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-02T00:19:57.698Z</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>363</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2752</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>46144.01540462963</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>46144.01708170139</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>900</v>
+      </c>
+      <c r="R11" t="n">
+        <v>133</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>379</v>
+      </c>
+      <c r="U11" t="n">
+        <v>144.899</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>L2_English</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>36931</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chinese (Simplified)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>task_b</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Invalid Response, Less Than 50 Words: 随着城市人口的快速增长，基础设施和公共服务面临着巨大的压力。政府需要采取有效的政策措施来管理城市人口过剩，同时保持经济机会和生活质量。以下列举了两种可能解决方案：
+1. 发展卫星城
+- 支持理由: 发展卫星城可以分散城市人口，缓解城市中心压力。通过在城市周边建设卫星城，可以降低基础设施和公共服务需求集中于中心城区，避免过度拥挤。
+- 示例: 北京的通州卫星城，是缓解北京中心城区的人口压力的一个例子。
+- 局限性: 卫星城建设需要大量资金投入，并且可能面临交通不便的问题。
+2. 提高城市基础设施建设
+- 支持理由: 通过加强城市基础设施建设，可以提高城市的承载能力，满足人口增长的需求。例如，上海的地铁网络建设，有效缓解了城市交通拥堵问题。
+- 示例: 上海地铁的快速发展，缓解了城市交通压力，为市民提供了便捷高效的出行方式。
+- 局限性: 基础设施建设需要长期投入和持续维护，并且可能面临技术瓶颈和资金不足的问题。</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-02T00:25:06.933Z</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>41</v>
+      </c>
+      <c r="I12" t="n">
+        <v>456</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>46144.01828962963</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>46144.01923689815</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>534</v>
+      </c>
+      <c r="R12" t="n">
+        <v>47</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>36</v>
+      </c>
+      <c r="U12" t="n">
+        <v>81.84399999999999</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>L1_Native</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>qr762</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chinese (Simplified)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>task_b</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Invalid Response, Less Than 50 Words: 政府可以先改善公共交通但成本高、建设慢。可以发展卫星城，把公司、学校和医院分散到市中心外，减少核心城区压力。但如果周边工作机会不够，人们还是会回到市中心。政府也应增加可负担住房，但这需要长期资金支持。</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-02T00:29:59.693Z</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>138</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>46144.0222547338</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>46144.02335189815</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>879</v>
+      </c>
+      <c r="R13" t="n">
+        <v>81</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>45</v>
+      </c>
+      <c r="U13" t="n">
+        <v>94.795</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>L1_Native</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>qr762</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>task_a</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Governments could increase affordable housing supply by funding public housing and requiring new private projects to include below-market units. This would help low- and middle-income workers remain near jobs, schools, and transport. However, it requires public money and may face resistance from local residents or developers.
+Second policy is rent stabilization, which limits sudden rent increases while still allowing reasonable landlord profits. This can give tenants security and reduce displacement. The trade-off is that strict controls may discourage maintenance or new rental construction.
+Governments could also improve transport to cheaper suburbs, but this depends on reliable transit and job access.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-02T00:35:45.840Z</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>103</v>
+      </c>
+      <c r="I14" t="n">
+        <v>714</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>46144.02536778935</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>46144.02706435185</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>247</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1655</v>
+      </c>
+      <c r="R14" t="n">
+        <v>247</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>409</v>
+      </c>
+      <c r="U14" t="n">
+        <v>146.583</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>L2_English</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Jf926</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chinese (Simplified)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>task_b</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Invalid Response, Less Than 50 Words: ## 应对城市过度拥挤问题的政策思路
+城市人口增长快速，基础设施和公共服务面临压力，政府需要采取有效的措施来管理问题。以下介绍两种可能的解决方案:
+1. 综合利用现有资源，优化城市布局：
+依据: 许多发达城市通过加强城市规划、交通枢纽建设等方式，有效利用现有的基础设施资源，比如北京市和上海市都是很好的例子。
+具体措施:
+优化交通系统: 建设新的地铁线路、公共交通枢纽，提高公交车运营效率，并鼓励使用共享单车等绿色出行工具。
+规划绿地和公园: 增加公园、绿地数量，改善城市景观，同时提高空气质量和生活品质。
+发展“城中村”改造: 将旧城区进行改造，利用现有资源，促进经济发展和人口流动。例如，北京市在改造老城区中，利用原有的建筑资源，打造新的社区和商业区。
+局限性:
+需要政府投入大量资金和人力来进行规划和建设，且可能需要时间才能看到效果。
+并非所有城市都适合采用此方案，需要根据具体城市情况进行调整。
+2. 推动新技术和新的经济模式：
+依据: 随着科技发展，一些新技术和新模式可以帮助缓解城市拥挤问题，比如远程办公、人工智能等，这些技术可以降低城市人口密度，并提高生活质量。
+具体措施:
+鼓励远程办公: 政府可以通过政策支持和税收优惠来鼓励企业进行远程办公，减少通勤压力。
+利用人工智能技术: 开发智能交通系统、智能社区服务等，优化资源分配，提升城市效率。
+发展新经济模式: 例如，鼓励共享经济、智慧城市建设等，这些模式可以有效地利用资源，提高生活质量。
+局限性:
+新技术和新模式的开发需要时间和投入，且可能存在技术障碍和市场竞争问题。
+总而言之，政府应该根据城市情况和发展阶段选择合适的解决方案，并结合多种政策措施来有效应对城市过度拥挤问题。 同时，还需要加强公众意识和参与度，鼓励市民积极参与到解决问题中来。</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-02T00:43:47.235Z</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>78</v>
+      </c>
+      <c r="I15" t="n">
+        <v>795</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>46144.03194806713</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>46144.03341384259</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>223</v>
+      </c>
+      <c r="R15" t="n">
+        <v>15</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>72</v>
+      </c>
+      <c r="U15" t="n">
+        <v>126.643</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>L1_Native</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jf926</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>task_b</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.  Investing in Smart Infrastructure &amp; Sustainable Development:
+Reasoning: This approach focuses on building and optimizing existing infrastructure for increased density and efficiency. It prioritizes sustainable urban development practices like compact city designs, green spaces, efficient public transport systems, and resource-saving technologies.
+Example: Implementing smart grids to optimize energy use in buildings.
+Benefits: Improved transportation networks reduce congestion, leading to faster commute times and less stress on the environment. This also fosters a more vibrant city center with enhanced walkability and mixed-use developments.
+Limitations/Trade-offs:
+Costly investment: Building new infrastructure requires substantial financial commitments.
+Slower progress: Implementing sustainable development can be slow, potentially leading to increased congestion and dependence on outdated infrastructure before significant improvements are made.
+2. Empowering Local Communities &amp; Promoting Social Inclusion:
+Reasoning: This approach focuses on empowering communities to develop solutions tailored to their needs. It prioritizes social inclusion, ensuring everyone benefits from the city's growth.
+Example: Supporting community-based initiatives for affordable housing development in underprivileged areas.
+Benefits: This fosters local ownership and encourages collaboration between residents, businesses, and policymakers. This approach can help mitigate social inequalities and create a more inclusive environment.
+Limitations/Trade-offs:
+Coordination challenges: Coordinating diverse community needs and resources requires effective communication and coordination.
+Uneven distribution of benefits: If not implemented strategically, this approach may not guarantee equal access to opportunities for all demographics within the city.
+Overall: The best policy solution will likely be a combination of these approaches. It's crucial to implement comprehensive strategies that address both infrastructure needs and community-specific challenges while ensuring economic opportunity and quality of life for everyone.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-05-02T00:50:13.412Z</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>268</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2128</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>46144.03573744213</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>46144.03697704861</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>761</v>
+      </c>
+      <c r="R16" t="n">
+        <v>110</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>308</v>
+      </c>
+      <c r="U16" t="n">
+        <v>107.102</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>L2_English</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>N / A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>task_b</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Urban Population Growth Management Outline
+I. Introduction
+• Context: Rapid urbanization leads to infrastructure strain and declining public services.
+• Core Goal: Balancing economic opportunities with high quality of life.
+II. Solution 1: Investment in Satellite Cities and Decentralization
+• Reasoning: Developing secondary hubs diverts population flow away from the overcrowded city center.
+• Examples: Creating high-tech industrial zones in suburbs or nearby towns to provide jobs locally.
+• Limitations: High initial infrastructure costs and the risk of "ghost towns" if businesses are not incentivized to move.
+III. Solution 2: Implementation of Smart City Infrastructure and Public Transit
+• Reasoning: Using technology to optimize resource allocation (water, power, traffic) increases efficiency in high-density areas.
+• Examples: Expanding high-speed rail and subway networks to reduce reliance on private cars and alleviate congestion.
+• Limitations: Data privacy concerns regarding smart monitoring and potential displacement of low-income residents during redevelopment.
+IV. Evaluation &amp; Conclusion
+• Policies must combine decentralization with technological upgrades to ensure sustainable urban expansion without sacrificing livability.</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-02T02:07:53.436Z</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>161</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1249</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>L2_English</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>N / A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Chinese (Simplified)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>task_a</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Invalid Response, Less Than 50 Words: 城市住房负担能力政策建议大纲
+一、 核心问题陈述
+• 许多城市房价增长速度远超收入增速，导致居民难以负担适宜住房，影响社会公平与经济稳定。
+二、 政策方案一：增加包容性住房供应（Inclusionary Zoning）
+• 具体措施： 强制要求房地产开发商在新项目中保留一定比例的低价房或廉租房，以换取开发许可。
+• 支持理由： 能够直接在核心地段增加针对中低收入人群的住房供应。
+• 局限与折衷： 可能导致开发商利润缩减，进而将成本转嫁给购买商品房的市场价客户。
+三、 政策方案二：政府提供租房补贴与财政支持
+• 具体措施： 对符合条件的家庭直接发放租房代金券或提供利息较低的购房贷款支持。
+• 支持理由： 能够迅速缓解低收入人群的经济压力，增加其在租房市场上的竞争力。
+• 局限与折衷： 如果房屋供应总量没有增加，此类补贴可能会推高整体房租，且对政府财政预算构成压力。
+四、 总结评估
+• 政府应结合“增加土地供应”与“金融政策调节”，在不破坏市场经济活力的前提下，多管齐下解决住房危机。</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-02T02:09:23.693Z</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>45</v>
+      </c>
+      <c r="I18" t="n">
+        <v>484</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>L1_Native</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>02135</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>task_a</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Solution 1: Incentivizing Housing Supply Development
+Policy: Subsidizing developers to build affordable units in high-demand areas. This could take various forms like tax breaks, grants, or direct financial assistance for construction of mixed-income housing projects.
+Reasoning: This directly addresses the supply side issue. By increasing the number of available homes (especially those within a target price range), it can reduce competition and make affordable options more accessible. Studies have shown that increased density and diverse housing development can be effective in boosting affordability.
+Potential Limitations/Trade-offs:
+Political feasibility: Securing political support for large-scale subsidies can be challenging, especially if funding sources are debated.
+Long term impact: While immediate benefits might be seen, the full effect of building affordable units takes time to materialize. It's crucial to have a long-term strategy and ensure these units are truly accessible for low-income families.
+Solution 2: Government-Facilitated Co-Ownership Housing
+Policy: Implement a policy that allows governments to purchase or lease land in areas with high demand, then develop affordable housing through co-ownership models.
+This could involve establishing cooperatives where residents share ownership of buildings and benefit from lower rents compared to private market rental rates. It can also include options for rent-to-own agreements or long-term leases.
+Reasoning: This provides direct government control over the housing process, ensuring affordability is prioritized within the development. The co-ownership model fosters community engagement and shared responsibility, which could lead to a more stable housing market. It allows governments to directly influence housing quality and design while promoting equitable access to homes.
+Potential Limitations/Trade-offs:
+Administrative complexity: Managing complex co-owned housing ventures requires extensive planning, legal framework development, and clear guidelines on resident participation and governance. This could lead to delays in implementation.
+Scale limitations: Government involvement might be limited by existing infrastructure and funding constraints. It's crucial for governments to adopt a phased approach, ensuring the viability of these initiatives before widespread implementation.
+Both of these solutions have potential but require careful consideration. A combination of strategies, tailored to specific local contexts, could provide a more comprehensive approach to tackling housing affordability issues.</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-02T03:03:10.423Z</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>362</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2615</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>46144.13013903935</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>46144.13175704861</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1457</v>
+      </c>
+      <c r="R19" t="n">
+        <v>222</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>375</v>
+      </c>
+      <c r="U19" t="n">
+        <v>139.796</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>L2_English</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>02135</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chinese (Simplified)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>task_b</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Invalid Response, Less Than 50 Words: 1. 住房补贴政策:
+方案原理: 政府直接或间接为符合条件的低收入群体提供住房补贴，鼓励房东出租房屋、增加租房供给量。
+支持理由: 通过提高租房市场竞争力，可以缓解房价上涨压力，让更多人能够负担居住成本，减少拥挤现象。
+例子: 例如，政府可以根据收入水平和家庭规模提供住房补贴，鼓励部分低收入群体入住公共房屋或租赁公寓。
+潜在局限性: 补贴政策需要政府财政投入，并可能存在滥用问题，难以实现精准扶助。
+2. 政府-居民共性产权房屋政策:
+方案原理: 政府利用土地资源，与居民共同开发建设房屋，形成“政府-居民共性”的房屋项目。
+支持理由: 这可以有效缓解房价上涨压力，同时保障居民居住需求，并增加公共服务设施的投入和管理效率。
+例子: 政府可以采取土地合作模式，与居民共同开发小区，并在小区内建设公共服务设施，如公园、社区中心等。
+潜在局限性: 政府-居民共性房屋项目的实施需要制定详细的技术方案和法律法规，以及政府和居民的合作机制，也可能存在资金投入和土地利用问题。</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-02T03:10:40.865Z</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>50</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>46144.13324203704</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>46144.1345897338</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>853</v>
+      </c>
+      <c r="R20" t="n">
+        <v>118</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>63</v>
+      </c>
+      <c r="U20" t="n">
+        <v>116.441</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>L1_Native</t>
         </is>
@@ -1087,7 +2307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1265,62 +2485,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>33841</t>
+          <t>02135</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>63.33333333333334</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
-        <v>59.5</v>
+        <v>222</v>
       </c>
       <c r="G2" t="n">
-        <v>3.833333333333336</v>
+        <v>-104</v>
       </c>
       <c r="H2" t="n">
-        <v>190</v>
+        <v>118</v>
       </c>
       <c r="I2" t="n">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="J2" t="n">
-        <v>-48</v>
+        <v>-104</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>597</v>
+        <v>63</v>
       </c>
       <c r="O2" t="n">
-        <v>956</v>
+        <v>375</v>
       </c>
       <c r="P2" t="n">
-        <v>-359</v>
+        <v>-312</v>
       </c>
       <c r="Q2" t="n">
-        <v>532.634</v>
+        <v>116.441</v>
       </c>
       <c r="R2" t="n">
-        <v>478.618</v>
+        <v>139.796</v>
       </c>
       <c r="S2" t="n">
-        <v>54.01600000000002</v>
+        <v>-23.35499999999999</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -1332,22 +2552,22 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="X2" t="n">
-        <v>200</v>
+        <v>362</v>
       </c>
       <c r="Y2" t="n">
-        <v>-30</v>
+        <v>-312</v>
       </c>
       <c r="Z2" t="n">
-        <v>659</v>
+        <v>481</v>
       </c>
       <c r="AA2" t="n">
-        <v>1314</v>
+        <v>2615</v>
       </c>
       <c r="AB2" t="n">
-        <v>-655</v>
+        <v>-2134</v>
       </c>
       <c r="AC2" t="n">
         <v>2</v>
@@ -1371,62 +2591,62 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UID-1776989058197-147na</t>
+          <t>33841</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E3" t="n">
-        <v>157</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>59.5</v>
       </c>
       <c r="G3" t="n">
-        <v>71</v>
+        <v>3.833333333333336</v>
       </c>
       <c r="H3" t="n">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="I3" t="n">
-        <v>86</v>
+        <v>238</v>
       </c>
       <c r="J3" t="n">
-        <v>71</v>
+        <v>-48</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N3" t="n">
-        <v>417</v>
+        <v>597</v>
       </c>
       <c r="O3" t="n">
-        <v>375</v>
+        <v>956</v>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
+        <v>-359</v>
       </c>
       <c r="Q3" t="n">
-        <v>90.169</v>
+        <v>532.634</v>
       </c>
       <c r="R3" t="n">
-        <v>81.886</v>
+        <v>478.618</v>
       </c>
       <c r="S3" t="n">
-        <v>8.283000000000001</v>
+        <v>54.01600000000002</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -1438,22 +2658,22 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>337</v>
+        <v>170</v>
       </c>
       <c r="X3" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="Y3" t="n">
-        <v>155</v>
+        <v>-30</v>
       </c>
       <c r="Z3" t="n">
-        <v>1538</v>
+        <v>659</v>
       </c>
       <c r="AA3" t="n">
-        <v>1341</v>
+        <v>1314</v>
       </c>
       <c r="AB3" t="n">
-        <v>197</v>
+        <v>-655</v>
       </c>
       <c r="AC3" t="n">
         <v>2</v>
@@ -1477,107 +2697,743 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>36862</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>74</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-58</v>
+      </c>
+      <c r="H4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" t="n">
+        <v>74</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-58</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>58</v>
+      </c>
+      <c r="O4" t="n">
+        <v>374</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-316</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>104.337</v>
+      </c>
+      <c r="R4" t="n">
+        <v>116.579</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-12.24199999999999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>124</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-118</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>876</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-840</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>36931</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F5" t="n">
+        <v>133</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-86</v>
+      </c>
+      <c r="H5" t="n">
+        <v>47</v>
+      </c>
+      <c r="I5" t="n">
+        <v>133</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-86</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>36</v>
+      </c>
+      <c r="O5" t="n">
+        <v>379</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-343</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>81.84399999999999</v>
+      </c>
+      <c r="R5" t="n">
+        <v>144.899</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-63.05500000000001</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>41</v>
+      </c>
+      <c r="X5" t="n">
+        <v>363</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-322</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>456</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2752</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-2296</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jf926</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" t="n">
+        <v>110</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-95</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>110</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-95</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>72</v>
+      </c>
+      <c r="O6" t="n">
+        <v>308</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-236</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>126.643</v>
+      </c>
+      <c r="R6" t="n">
+        <v>107.102</v>
+      </c>
+      <c r="S6" t="n">
+        <v>19.541</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>78</v>
+      </c>
+      <c r="X6" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-190</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>795</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2128</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-1333</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>N / A</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>161</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-116</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>484</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1249</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-765</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UID-1776989058197-147na</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>157</v>
+      </c>
+      <c r="F8" t="n">
+        <v>86</v>
+      </c>
+      <c r="G8" t="n">
+        <v>71</v>
+      </c>
+      <c r="H8" t="n">
+        <v>157</v>
+      </c>
+      <c r="I8" t="n">
+        <v>86</v>
+      </c>
+      <c r="J8" t="n">
+        <v>71</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>417</v>
+      </c>
+      <c r="O8" t="n">
+        <v>375</v>
+      </c>
+      <c r="P8" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>90.169</v>
+      </c>
+      <c r="R8" t="n">
+        <v>81.886</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8.283000000000001</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>337</v>
+      </c>
+      <c r="X8" t="n">
+        <v>182</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>155</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1538</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1341</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>197</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>UID-1777303111836-827na</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>44</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F9" t="n">
         <v>48</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G9" t="n">
         <v>-4</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H9" t="n">
         <v>44</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I9" t="n">
         <v>48</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J9" t="n">
         <v>-4</v>
       </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>146</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O9" t="n">
         <v>407</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P9" t="n">
         <v>-261</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q9" t="n">
         <v>62.813</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R9" t="n">
         <v>99.42400000000001</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S9" t="n">
         <v>-36.611</v>
       </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
         <v>145</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X9" t="n">
         <v>108</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y9" t="n">
         <v>37</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z9" t="n">
         <v>568</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA9" t="n">
         <v>825</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AB9" t="n">
         <v>-257</v>
       </c>
-      <c r="AC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>qr762</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" t="n">
+        <v>247</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-166</v>
+      </c>
+      <c r="H10" t="n">
+        <v>81</v>
+      </c>
+      <c r="I10" t="n">
+        <v>247</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-166</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>45</v>
+      </c>
+      <c r="O10" t="n">
+        <v>409</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-364</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>94.795</v>
+      </c>
+      <c r="R10" t="n">
+        <v>146.583</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-51.788</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>16</v>
+      </c>
+      <c r="X10" t="n">
+        <v>103</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-87</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>714</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-576</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -1633,19 +3489,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.666666666666667</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1111111111111111</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4226497308103743</v>
+        <v>0.3465935070873342</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -1658,22 +3514,22 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88.11111111111113</v>
+        <v>60.14814814814815</v>
       </c>
       <c r="B3" t="n">
-        <v>64.5</v>
+        <v>108.8333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>23.61111111111111</v>
+        <v>-48.68518518518518</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4257506503804366</v>
+        <v>0.07827104752247457</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75</v>
+        <v>0.078125</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1683,22 +3539,22 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130.3333333333333</v>
+        <v>74.22222222222223</v>
       </c>
       <c r="B4" t="n">
-        <v>124</v>
+        <v>128.6666666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>6.333333333333333</v>
+        <v>-54.44444444444444</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8721429839047605</v>
+        <v>0.04711205879041275</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.0546875</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1708,19 +3564,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.666666666666667</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1111111111111111</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4226497308103743</v>
+        <v>0.3465935070873342</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -1733,22 +3589,22 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>386.6666666666667</v>
+        <v>159.3333333333333</v>
       </c>
       <c r="B6" t="n">
-        <v>579.3333333333334</v>
+        <v>398.1111111111111</v>
       </c>
       <c r="C6" t="n">
-        <v>-192.6666666666667</v>
+        <v>-238.7777777777778</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2514924900745041</v>
+        <v>0.001614003790017368</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.015625</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1758,22 +3614,22 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>228.5386666666667</v>
+        <v>134.4084444444445</v>
       </c>
       <c r="B7" t="n">
-        <v>219.976</v>
+        <v>146.0985555555556</v>
       </c>
       <c r="C7" t="n">
-        <v>8.562666666666672</v>
+        <v>-11.69011111111111</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7745287410506582</v>
+        <v>0.3684509925110652</v>
       </c>
       <c r="F7" t="n">
-        <v>0.75</v>
+        <v>0.3828125</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1792,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -1804,22 +3660,22 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>217.3333333333333</v>
+        <v>98.66666666666667</v>
       </c>
       <c r="B9" t="n">
-        <v>163.3333333333333</v>
+        <v>207.8888888888889</v>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>-109.2222222222222</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4231989292958646</v>
+        <v>0.06676509894267832</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.09765625</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1829,22 +3685,22 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>921.6666666666666</v>
+        <v>572.7777777777778</v>
       </c>
       <c r="B10" t="n">
-        <v>1160</v>
+        <v>1534.888888888889</v>
       </c>
       <c r="C10" t="n">
-        <v>-238.3333333333333</v>
+        <v>-962.1111111111111</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4350339273503294</v>
+        <v>0.00803125066460179</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>0.0078125</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1854,22 +3710,22 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="B11" t="n">
-        <v>1.333333333333333</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6666666666666666</v>
+        <v>-0.2222222222222222</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4226497308103743</v>
+        <v>0.6223833291543434</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.8125</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1879,19 +3735,23 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0.1111111111111111</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5942640159772071</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>has_tradeoff</t>
@@ -1909,7 +3769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV9"/>
+  <dimension ref="A1:AV11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3309,6 +5169,302 @@
       </c>
       <c r="AV9" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>N / A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>02135</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Native language</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.666666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -3364,22 +5520,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.61904761904762</v>
+        <v>5.407407407407407</v>
       </c>
       <c r="B2" t="n">
-        <v>5.142857142857143</v>
+        <v>4.888888888888889</v>
       </c>
       <c r="C2" t="n">
-        <v>0.476190476190476</v>
+        <v>0.5185185185185184</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4025739816280322</v>
+        <v>0.2361816347973192</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6875</v>
+        <v>0.3125</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3389,22 +5545,22 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5.142857142857141</v>
+        <v>5.074074074074074</v>
       </c>
       <c r="B3" t="n">
-        <v>5.190476190476191</v>
+        <v>4.925925925925926</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04761904761904777</v>
+        <v>0.148148148148148</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8867966519320479</v>
+        <v>0.6223833291543437</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75</v>
+        <v>0.9140625</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3414,22 +5570,22 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.190476190476191</v>
+        <v>4.888888888888889</v>
       </c>
       <c r="B4" t="n">
-        <v>5.38095238095238</v>
+        <v>4.962962962962963</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1904761904761904</v>
+        <v>-0.07407407407407406</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1030461731795406</v>
+        <v>0.5587899692492142</v>
       </c>
       <c r="F4" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3439,22 +5595,22 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4.238095238095238</v>
+        <v>4.111111111111112</v>
       </c>
       <c r="B5" t="n">
-        <v>4.285714285714286</v>
+        <v>4.074074074074074</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.04761904761904789</v>
+        <v>0.03703703703703681</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9241042981230824</v>
+        <v>0.9236558258378292</v>
       </c>
       <c r="F5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3467,19 +5623,19 @@
         <v>4.666666666666667</v>
       </c>
       <c r="B6" t="n">
-        <v>4.61904761904762</v>
+        <v>4.481481481481481</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04761904761904764</v>
+        <v>0.1851851851851853</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8805362023620852</v>
+        <v>0.4785612389891751</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8125</v>
+        <v>0.328125</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3498,7 +5654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC4"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3911,313 +6067,309 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>33841</t>
+          <t>02135</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>118</v>
+      </c>
+      <c r="F2" t="n">
+        <v>222</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H2" t="n">
+        <v>118</v>
+      </c>
+      <c r="I2" t="n">
+        <v>222</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-104</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O2" t="n">
+        <v>375</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-312</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>116.441</v>
+      </c>
+      <c r="R2" t="n">
+        <v>139.796</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-23.35499999999999</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>50</v>
+      </c>
+      <c r="X2" t="n">
+        <v>362</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-312</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>481</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2615</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-2134</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Native language</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>63.33333333333334</v>
-      </c>
-      <c r="F2" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.833333333333336</v>
-      </c>
-      <c r="H2" t="n">
-        <v>190</v>
-      </c>
-      <c r="I2" t="n">
-        <v>238</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-48</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="AX2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD2" t="n">
         <v>3</v>
       </c>
-      <c r="L2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>597</v>
-      </c>
-      <c r="O2" t="n">
-        <v>956</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-359</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>532.634</v>
-      </c>
-      <c r="R2" t="n">
-        <v>478.618</v>
-      </c>
-      <c r="S2" t="n">
-        <v>54.01600000000002</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>170</v>
-      </c>
-      <c r="X2" t="n">
-        <v>200</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>659</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1314</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-655</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>Though I speak Korean natively, all my education was in English so it was easier to create ideas, prompt AI, assess AI's ideas, then adapt them into my own outline compared to Korean (in which typically only have casual conversations, nothing technical)</t>
-        </is>
-      </c>
-      <c r="AK2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="BE2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI2" t="n">
         <v>4.333333333333333</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="BJ2" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CA2" t="n">
         <v>4.666666666666667</v>
       </c>
-      <c r="AS2" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>4.333333333333333</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>3.333333333333333</v>
-      </c>
       <c r="CB2" t="n">
-        <v>3.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="CC2" t="n">
-        <v>0</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UID-1776989058197-147na</t>
+          <t>33841</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E3" t="n">
-        <v>157</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>59.5</v>
       </c>
       <c r="G3" t="n">
-        <v>71</v>
+        <v>3.833333333333336</v>
       </c>
       <c r="H3" t="n">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="I3" t="n">
-        <v>86</v>
+        <v>238</v>
       </c>
       <c r="J3" t="n">
-        <v>71</v>
+        <v>-48</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N3" t="n">
-        <v>417</v>
+        <v>597</v>
       </c>
       <c r="O3" t="n">
-        <v>375</v>
+        <v>956</v>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
+        <v>-359</v>
       </c>
       <c r="Q3" t="n">
-        <v>90.169</v>
+        <v>532.634</v>
       </c>
       <c r="R3" t="n">
-        <v>81.886</v>
+        <v>478.618</v>
       </c>
       <c r="S3" t="n">
-        <v>8.283000000000001</v>
+        <v>54.01600000000002</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -4229,22 +6381,22 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>337</v>
+        <v>170</v>
       </c>
       <c r="X3" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="Y3" t="n">
-        <v>155</v>
+        <v>-30</v>
       </c>
       <c r="Z3" t="n">
-        <v>1538</v>
+        <v>659</v>
       </c>
       <c r="AA3" t="n">
-        <v>1341</v>
+        <v>1314</v>
       </c>
       <c r="AB3" t="n">
-        <v>197</v>
+        <v>-655</v>
       </c>
       <c r="AC3" t="n">
         <v>2</v>
@@ -4264,206 +6416,1698 @@
       <c r="AH3" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
-      <c r="CC3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Though I speak Korean natively, all my education was in English so it was easier to create ideas, prompt AI, assess AI's ideas, then adapt them into my own outline compared to Korean (in which typically only have casual conversations, nothing technical)</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>36862</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>74</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-58</v>
+      </c>
+      <c r="H4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" t="n">
+        <v>74</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-58</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>58</v>
+      </c>
+      <c r="O4" t="n">
+        <v>374</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-316</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>104.337</v>
+      </c>
+      <c r="R4" t="n">
+        <v>116.579</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-12.24199999999999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>124</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-118</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>876</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-840</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>I think I preferred English because I have been using English to interact with GENAI on a normal basis, therefore it felt more natural to me. Also normally, I would use a combination of Chinese(my native language) and english to describe the prompt which to me it feel the most efficient.</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>36931</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F5" t="n">
+        <v>133</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-86</v>
+      </c>
+      <c r="H5" t="n">
+        <v>47</v>
+      </c>
+      <c r="I5" t="n">
+        <v>133</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-86</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>36</v>
+      </c>
+      <c r="O5" t="n">
+        <v>379</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-343</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>81.84399999999999</v>
+      </c>
+      <c r="R5" t="n">
+        <v>144.899</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-63.05500000000001</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>41</v>
+      </c>
+      <c r="X5" t="n">
+        <v>363</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-322</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>456</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2752</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-2296</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>No preference</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>6</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jf926</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" t="n">
+        <v>110</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-95</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>110</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-95</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>72</v>
+      </c>
+      <c r="O6" t="n">
+        <v>308</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-236</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>126.643</v>
+      </c>
+      <c r="R6" t="n">
+        <v>107.102</v>
+      </c>
+      <c r="S6" t="n">
+        <v>19.541</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>78</v>
+      </c>
+      <c r="X6" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-190</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>795</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2128</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-1333</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>No preference</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>N / A</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>161</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-116</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>484</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1249</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-765</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>4</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UID-1776989058197-147na</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>157</v>
+      </c>
+      <c r="F8" t="n">
+        <v>86</v>
+      </c>
+      <c r="G8" t="n">
+        <v>71</v>
+      </c>
+      <c r="H8" t="n">
+        <v>157</v>
+      </c>
+      <c r="I8" t="n">
+        <v>86</v>
+      </c>
+      <c r="J8" t="n">
+        <v>71</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>417</v>
+      </c>
+      <c r="O8" t="n">
+        <v>375</v>
+      </c>
+      <c r="P8" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>90.169</v>
+      </c>
+      <c r="R8" t="n">
+        <v>81.886</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8.283000000000001</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>337</v>
+      </c>
+      <c r="X8" t="n">
+        <v>182</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>155</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1538</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1341</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>197</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>UID-1777303111836-827na</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>44</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F9" t="n">
         <v>48</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G9" t="n">
         <v>-4</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H9" t="n">
         <v>44</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I9" t="n">
         <v>48</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J9" t="n">
         <v>-4</v>
       </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>146</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O9" t="n">
         <v>407</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P9" t="n">
         <v>-261</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q9" t="n">
         <v>62.813</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R9" t="n">
         <v>99.42400000000001</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S9" t="n">
         <v>-36.611</v>
       </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
         <v>145</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X9" t="n">
         <v>108</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y9" t="n">
         <v>37</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z9" t="n">
         <v>568</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA9" t="n">
         <v>825</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AB9" t="n">
         <v>-257</v>
       </c>
-      <c r="AC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr"/>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>qr762</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" t="n">
+        <v>247</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-166</v>
+      </c>
+      <c r="H10" t="n">
+        <v>81</v>
+      </c>
+      <c r="I10" t="n">
+        <v>247</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-166</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>45</v>
+      </c>
+      <c r="O10" t="n">
+        <v>409</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-364</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>94.795</v>
+      </c>
+      <c r="R10" t="n">
+        <v>146.583</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-51.788</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>16</v>
+      </c>
+      <c r="X10" t="n">
+        <v>103</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-87</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>714</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-576</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Native language</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>1.333333333333333</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
